--- a/COMPARE_RESULTS/DAO_vs_All_Time_Wilcoxon.xlsx
+++ b/COMPARE_RESULTS/DAO_vs_All_Time_Wilcoxon.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,33 +415,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Instance</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AO_no_hybrid</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Original_GA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>GA_TABU</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>GWO</t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ABC_TABU</t>
         </is>
       </c>
     </row>
@@ -465,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -475,10 +468,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -492,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,10 +500,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -519,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,10 +532,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -546,7 +554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -556,10 +564,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -573,7 +586,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -583,10 +596,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -600,7 +618,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -610,10 +628,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -627,7 +650,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -637,10 +660,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -654,7 +682,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -664,10 +692,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -681,7 +714,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -691,10 +724,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -708,7 +746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -718,10 +756,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -735,7 +778,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -745,10 +788,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -762,7 +810,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -772,10 +820,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -789,7 +842,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -799,10 +852,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -816,12 +874,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -830,6 +888,11 @@
         </is>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -846,33 +909,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Instance</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AO_no_hybrid</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Original_GA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>GA_TABU</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>GWO</t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ABC_TABU</t>
         </is>
       </c>
     </row>
@@ -894,6 +962,9 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -913,6 +984,9 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -932,6 +1006,9 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -951,6 +1028,9 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -970,6 +1050,9 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -989,6 +1072,9 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1008,6 +1094,9 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1027,6 +1116,9 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1046,6 +1138,9 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1065,6 +1160,9 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1084,6 +1182,9 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1103,6 +1204,9 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1122,6 +1226,9 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1133,12 +1240,15 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.00032</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1153,38 +1263,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Instance</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DAO_Mean</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>AO_no_hybrid_Mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>Original_GA_Mean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>GA_TABU_Mean</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ABC_Mean</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>GWO_Mean</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ABC_TABU_Mean</t>
         </is>
       </c>
     </row>
@@ -1198,16 +1313,19 @@
         <v>12.3049</v>
       </c>
       <c r="C2" t="n">
+        <v>7.3024</v>
+      </c>
+      <c r="D2" t="n">
         <v>24.431</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>13.6729</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>8.994899999999999</v>
       </c>
-      <c r="F2" t="n">
-        <v>79.73180000000001</v>
+      <c r="G2" t="n">
+        <v>23.3511</v>
       </c>
     </row>
     <row r="3">
@@ -1220,16 +1338,19 @@
         <v>12.3062</v>
       </c>
       <c r="C3" t="n">
+        <v>7.7947</v>
+      </c>
+      <c r="D3" t="n">
         <v>24.3847</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>13.6144</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>8.9777</v>
       </c>
-      <c r="F3" t="n">
-        <v>79.2694</v>
+      <c r="G3" t="n">
+        <v>23.352</v>
       </c>
     </row>
     <row r="4">
@@ -1242,16 +1363,19 @@
         <v>12.1848</v>
       </c>
       <c r="C4" t="n">
+        <v>8.082800000000001</v>
+      </c>
+      <c r="D4" t="n">
         <v>24.2136</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>13.5298</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>8.9002</v>
       </c>
-      <c r="F4" t="n">
-        <v>79.0843</v>
+      <c r="G4" t="n">
+        <v>23.2422</v>
       </c>
     </row>
     <row r="5">
@@ -1264,16 +1388,19 @@
         <v>12.2505</v>
       </c>
       <c r="C5" t="n">
+        <v>7.7528</v>
+      </c>
+      <c r="D5" t="n">
         <v>24.3926</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>13.8095</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>9.0219</v>
       </c>
-      <c r="F5" t="n">
-        <v>79.43089999999999</v>
+      <c r="G5" t="n">
+        <v>23.4931</v>
       </c>
     </row>
     <row r="6">
@@ -1286,16 +1413,19 @@
         <v>12.4745</v>
       </c>
       <c r="C6" t="n">
+        <v>7.8591</v>
+      </c>
+      <c r="D6" t="n">
         <v>24.6922</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>14.0623</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>9.142200000000001</v>
       </c>
-      <c r="F6" t="n">
-        <v>79.95529999999999</v>
+      <c r="G6" t="n">
+        <v>23.7097</v>
       </c>
     </row>
     <row r="7">
@@ -1308,16 +1438,19 @@
         <v>12.2962</v>
       </c>
       <c r="C7" t="n">
+        <v>7.8445</v>
+      </c>
+      <c r="D7" t="n">
         <v>24.7125</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>13.9278</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>9.081799999999999</v>
       </c>
-      <c r="F7" t="n">
-        <v>79.4064</v>
+      <c r="G7" t="n">
+        <v>23.3912</v>
       </c>
     </row>
     <row r="8">
@@ -1330,16 +1463,19 @@
         <v>12.3976</v>
       </c>
       <c r="C8" t="n">
+        <v>7.861</v>
+      </c>
+      <c r="D8" t="n">
         <v>24.4739</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>13.6722</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>9.011799999999999</v>
       </c>
-      <c r="F8" t="n">
-        <v>79.4631</v>
+      <c r="G8" t="n">
+        <v>23.3278</v>
       </c>
     </row>
     <row r="9">
@@ -1352,16 +1488,19 @@
         <v>19.4664</v>
       </c>
       <c r="C9" t="n">
+        <v>12.6662</v>
+      </c>
+      <c r="D9" t="n">
         <v>37.8624</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>21.2407</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>13.7217</v>
       </c>
-      <c r="F9" t="n">
-        <v>121.0595</v>
+      <c r="G9" t="n">
+        <v>35.8206</v>
       </c>
     </row>
     <row r="10">
@@ -1374,16 +1513,19 @@
         <v>19.4532</v>
       </c>
       <c r="C10" t="n">
+        <v>12.7703</v>
+      </c>
+      <c r="D10" t="n">
         <v>37.8064</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>21.4085</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>13.7572</v>
       </c>
-      <c r="F10" t="n">
-        <v>126.3588</v>
+      <c r="G10" t="n">
+        <v>35.8038</v>
       </c>
     </row>
     <row r="11">
@@ -1396,16 +1538,19 @@
         <v>19.4166</v>
       </c>
       <c r="C11" t="n">
+        <v>12.7656</v>
+      </c>
+      <c r="D11" t="n">
         <v>38.296</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>21.1895</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>13.7973</v>
       </c>
-      <c r="F11" t="n">
-        <v>126.7127</v>
+      <c r="G11" t="n">
+        <v>35.5485</v>
       </c>
     </row>
     <row r="12">
@@ -1418,16 +1563,19 @@
         <v>19.509</v>
       </c>
       <c r="C12" t="n">
+        <v>12.7724</v>
+      </c>
+      <c r="D12" t="n">
         <v>38.1197</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>21.3246</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>13.9314</v>
       </c>
-      <c r="F12" t="n">
-        <v>126.9893</v>
+      <c r="G12" t="n">
+        <v>35.9862</v>
       </c>
     </row>
     <row r="13">
@@ -1440,16 +1588,19 @@
         <v>19.5565</v>
       </c>
       <c r="C13" t="n">
+        <v>12.8046</v>
+      </c>
+      <c r="D13" t="n">
         <v>38.3593</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>21.503</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>14.0373</v>
       </c>
-      <c r="F13" t="n">
-        <v>127.3316</v>
+      <c r="G13" t="n">
+        <v>36.165</v>
       </c>
     </row>
     <row r="14">
@@ -1462,16 +1613,19 @@
         <v>19.7489</v>
       </c>
       <c r="C14" t="n">
+        <v>12.7371</v>
+      </c>
+      <c r="D14" t="n">
         <v>37.9482</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>21.0968</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>13.7431</v>
       </c>
-      <c r="F14" t="n">
-        <v>126.5688</v>
+      <c r="G14" t="n">
+        <v>35.7532</v>
       </c>
     </row>
     <row r="15">
@@ -1484,16 +1638,19 @@
         <v>19.7219</v>
       </c>
       <c r="C15" t="n">
+        <v>12.8485</v>
+      </c>
+      <c r="D15" t="n">
         <v>38.3243</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>18.006</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>12.1125</v>
       </c>
-      <c r="F15" t="n">
-        <v>126.6305</v>
+      <c r="G15" t="n">
+        <v>33.3284</v>
       </c>
     </row>
   </sheetData>
